--- a/dcf/LMND.xlsx
+++ b/dcf/LMND.xlsx
@@ -361,77 +361,77 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 15.8x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -867,7 +867,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1122,184 +1122,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>12.8</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>27.42960303147738</v>
+        <v>35.44536080825692</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>26.40612174955237</v>
+        <v>34.06907419804948</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>25.43071214677194</v>
+        <v>32.75786537019523</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>24.5009141848209</v>
+        <v>31.50838394223291</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>23.61440441997433</v>
+        <v>30.31746640409791</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>22.76898783495442</v>
+        <v>29.18212490565475</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>21.96259019343097</v>
+        <v>28.09953676352092</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>13.8</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>29.53901297273515</v>
+        <v>37.55477074951471</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>28.4226881833674</v>
+        <v>36.08564063186453</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>27.35891036346228</v>
+        <v>34.68606358688557</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>26.34498517361353</v>
+        <v>33.35245493102554</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>25.37836810000685</v>
+        <v>32.08143008413045</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>24.45665548513872</v>
+        <v>30.86979255583905</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>23.57757613292832</v>
+        <v>29.71452270301828</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>14.8</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>31.64842291399293</v>
+        <v>39.66418069077248</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>30.43925461718243</v>
+        <v>38.10220706567956</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>29.28710858015261</v>
+        <v>36.61426180357591</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>28.18905616240616</v>
+        <v>35.19652591981817</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>27.14233178003937</v>
+        <v>33.84539376416297</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>26.14432313532302</v>
+        <v>32.55746020602334</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>25.19256207242568</v>
+        <v>31.32950864251563</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>33.7578328552507</v>
+        <v>41.77359063203025</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>32.45582105099746</v>
+        <v>40.11877349949459</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>31.21530679684295</v>
+        <v>38.54246002026624</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>30.0331271511988</v>
+        <v>37.04059690861081</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>28.9062954600719</v>
+        <v>35.60935744419549</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>27.83199078550731</v>
+        <v>34.24512785620765</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>26.80754801192303</v>
+        <v>32.94449458201299</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
+        <v>16.8</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>35.86724279650848</v>
+        <v>43.88300057328802</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>34.47238748481249</v>
+        <v>42.13533993330963</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>33.14350501353329</v>
+        <v>40.47065823695658</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>31.87719813999143</v>
+        <v>38.88466789740345</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>30.67025914010442</v>
+        <v>37.37332112422801</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>29.51965843569161</v>
+        <v>35.93279550639193</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>28.42253395142038</v>
+        <v>34.55948052151034</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
+        <v>17.8</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>37.97665273776625</v>
+        <v>45.99241051454581</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>36.48895391862752</v>
+        <v>44.15190636712466</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>35.07170323022363</v>
+        <v>42.39885645364693</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>33.72126912878407</v>
+        <v>40.72873888619608</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>32.43422282013695</v>
+        <v>39.13728480426053</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>31.20732608587591</v>
+        <v>37.62046315657623</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>30.03751989091775</v>
+        <v>36.1744664610077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
+        <v>18.8</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>40.08606267902404</v>
+        <v>48.10182045580358</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>38.50552035244257</v>
+        <v>46.16847280093969</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>36.99990144691398</v>
+        <v>44.32705467033727</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>35.5653401175767</v>
+        <v>42.57280987498871</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>34.19818650016947</v>
+        <v>40.90124848429305</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>32.8949937360602</v>
+        <v>39.30813080676054</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>31.65250583041511</v>
+        <v>37.78945240050506</v>
       </c>
     </row>
     <row r="13">
@@ -1322,7 +1322,7 @@
         <v>0.1233172681245544</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.7842832141513826</v>
+        <v>0.7537842868167569</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24369,7 +24369,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="46">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>30.0331271511988</v>
+        <v>37.04059690861081</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>48.58614144707017</v>
+        <v>58.61991047548324</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>17.10224071115422</v>
+        <v>21.74610643921449</v>
       </c>
     </row>
     <row r="59">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24806,7 +24806,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24825,7 +24829,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24833,7 +24837,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24852,7 +24860,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24860,7 +24868,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24879,7 +24891,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24887,7 +24899,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24906,7 +24922,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24914,7 +24930,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24933,7 +24953,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24941,7 +24961,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24960,7 +24984,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24968,7 +24992,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24987,7 +25015,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -24995,7 +25023,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25014,7 +25046,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25022,7 +25054,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25041,7 +25077,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25049,7 +25085,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25068,7 +25108,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25076,7 +25116,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25095,7 +25139,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25103,7 +25147,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25122,12 +25170,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.8x</t>
         </is>
       </c>
       <c r="F20" s="31" t="inlineStr"/>
@@ -25149,7 +25197,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25157,7 +25205,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25176,7 +25228,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/dcf/LMND.xlsx
+++ b/dcf/LMND.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.1083172681245544</v>
+        <v>0.1086109213660935</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.1133172681245544</v>
+        <v>0.1136109213660935</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.1183172681245544</v>
+        <v>0.1186109213660935</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1233172681245544</v>
+        <v>0.1236109213660935</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1283172681245544</v>
+        <v>0.1286109213660935</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1333172681245544</v>
+        <v>0.1336109213660935</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1383172681245544</v>
+        <v>0.1386109213660935</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>12.8</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>35.44536080825692</v>
+        <v>24.53820257675504</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>34.06907419804948</v>
+        <v>23.62654924533389</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>32.75786537019523</v>
+        <v>22.75803830272285</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>31.50838394223291</v>
+        <v>21.93045205146838</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>30.31746640409791</v>
+        <v>21.14169631547346</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>29.18212490565475</v>
+        <v>20.389793036755</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>28.09953676352092</v>
+        <v>19.67287334672094</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>13.8</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>37.55477074951471</v>
+        <v>25.92892074268698</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>36.08564063186453</v>
+        <v>24.95607219872641</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>34.68606358688557</v>
+        <v>24.02931504774745</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>33.35245493102554</v>
+        <v>23.14627723852737</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>32.08143008413045</v>
+        <v>22.30471895534721</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>30.86979255583905</v>
+        <v>21.50252468724093</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>29.71452270301828</v>
+        <v>20.73769580583012</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>14.8</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>39.66418069077248</v>
+        <v>27.31963890861892</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>38.10220706567956</v>
+        <v>26.28559515211893</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>36.61426180357591</v>
+        <v>25.30059179277205</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>35.19652591981817</v>
+        <v>24.36210242558637</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>33.84539376416297</v>
+        <v>23.46774159522095</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>32.55746020602334</v>
+        <v>22.61525633772687</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>31.32950864251563</v>
+        <v>21.80251826493931</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>15.8</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>41.77359063203025</v>
+        <v>28.71035707455086</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>40.11877349949459</v>
+        <v>27.61511810551145</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>38.54246002026624</v>
+        <v>26.57186853779664</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>37.04059690861081</v>
+        <v>25.57792761264536</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>35.60935744419549</v>
+        <v>24.63076423509469</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>34.24512785620765</v>
+        <v>23.7279879882128</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>32.94449458201299</v>
+        <v>22.86734072404849</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>16.8</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>43.88300057328802</v>
+        <v>30.1010752404828</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>42.13533993330963</v>
+        <v>28.94464105890397</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>40.47065823695658</v>
+        <v>27.84314528282124</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>38.88466789740345</v>
+        <v>26.79375279970436</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>37.37332112422801</v>
+        <v>25.79378687496843</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>35.93279550639193</v>
+        <v>24.84071963869873</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>34.55948052151034</v>
+        <v>23.93216318315767</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>17.8</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>45.99241051454581</v>
+        <v>31.49179340641474</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>44.15190636712466</v>
+        <v>30.27416401229649</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>42.39885645364693</v>
+        <v>29.11442202784584</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>40.72873888619608</v>
+        <v>28.00957798676335</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>39.13728480426053</v>
+        <v>26.95680951484218</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>37.62046315657623</v>
+        <v>25.95345128918467</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>36.1744664610077</v>
+        <v>24.99698564226685</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>18.8</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>48.10182045580358</v>
+        <v>32.88251157234668</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>46.16847280093969</v>
+        <v>31.603686965689</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>44.32705467033727</v>
+        <v>30.38569877287044</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>42.57280987498871</v>
+        <v>29.22540317382235</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>40.90124848429305</v>
+        <v>28.11983215471593</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>39.30813080676054</v>
+        <v>27.0661829396706</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>37.78945240050506</v>
+        <v>26.06180810137604</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>71.51999664306641</v>
+        <v>79.73999786376953</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1233172681245544</v>
+        <v>0.1236109213660935</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>15.8</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.7537842868167569</v>
+        <v>0.7712230693106017</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>71.51999664306641</v>
+        <v>79.73999786376953</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>37.04059690861081</v>
+        <v>25.57792761264536</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>58.61991047548324</v>
+        <v>39.48707789561357</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>21.74610643921449</v>
+        <v>15.44469867325419</v>
       </c>
     </row>
     <row r="59">
